--- a/testdata/realdata/onus.xlsx
+++ b/testdata/realdata/onus.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>用户</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>哈尔滨市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
           <t>哈尔滨市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +518,11 @@
           <t>大庆市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,6 +545,11 @@
           <t>大庆市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,6 +572,11 @@
           <t>齐齐哈尔市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,6 +599,11 @@
           <t>齐齐哈尔市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -591,6 +626,11 @@
           <t>牡丹江市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -613,6 +653,11 @@
           <t>牡丹江市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -635,6 +680,11 @@
           <t>佳木斯市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -655,6 +705,11 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>佳木斯市商务楼宇2号接入点（虚构演示）</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/onus.xlsx
+++ b/testdata/realdata/onus.xlsx
@@ -446,22 +446,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ONU-279116876-01</t>
+          <t>ONU-244077958-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OLT-279116876|0/1/1</t>
+          <t>OLT-244077958|0/1/1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>哈尔滨市商务楼宇1号接入点（虚构演示）</t>
+          <t>大庆市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,22 +473,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ONU-279116876-02</t>
+          <t>ONU-244077958-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OLT-279116876|0/1/2</t>
+          <t>OLT-244077958|0/1/2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>哈尔滨市商务楼宇2号接入点（虚构演示）</t>
+          <t>大庆市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -500,22 +500,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ONU-244077958-01</t>
+          <t>ONU-244081515-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OLT-244077958|0/1/1</t>
+          <t>OLT-244081515|0/1/1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大庆市商务楼宇1号接入点（虚构演示）</t>
+          <t>齐齐哈尔市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -527,22 +527,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ONU-244077958-02</t>
+          <t>ONU-244081515-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OLT-244077958|0/1/2</t>
+          <t>OLT-244081515|0/1/2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大庆市商务楼宇2号接入点（虚构演示）</t>
+          <t>齐齐哈尔市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -554,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ONU-244081515-01</t>
+          <t>ONU-279116876-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OLT-244081515|0/1/1</t>
+          <t>OLT-279116876|0/1/1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>齐齐哈尔市商务楼宇1号接入点（虚构演示）</t>
+          <t>哈尔滨市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -581,22 +581,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ONU-244081515-02</t>
+          <t>ONU-279116876-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OLT-244081515|0/1/2</t>
+          <t>OLT-279116876|0/1/2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>齐齐哈尔市商务楼宇2号接入点（虚构演示）</t>
+          <t>哈尔滨市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ONU-4059698545-01</t>
+          <t>ONU-304758391-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OLT-4059698545|0/1/1</t>
+          <t>OLT-304758391|0/1/1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>牡丹江市商务楼宇1号接入点（虚构演示）</t>
+          <t>佳木斯市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,22 +635,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ONU-4059698545-02</t>
+          <t>ONU-304758391-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OLT-4059698545|0/1/2</t>
+          <t>OLT-304758391|0/1/2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>牡丹江市商务楼宇2号接入点（虚构演示）</t>
+          <t>佳木斯市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,22 +662,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ONU-304758391-01</t>
+          <t>ONU-4059698545-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OLT-304758391|0/1/1</t>
+          <t>OLT-4059698545|0/1/1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>佳木斯市商务楼宇1号接入点（虚构演示）</t>
+          <t>牡丹江市商务楼宇1号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -689,22 +689,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ONU-304758391-02</t>
+          <t>ONU-4059698545-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OLT-304758391|0/1/2</t>
+          <t>OLT-4059698545|0/1/2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>佳木斯市商务楼宇2号接入点（虚构演示）</t>
+          <t>牡丹江市商务楼宇2号接入点（虚构演示）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
